--- a/TELEMETRYadcCLOCK/project/Post Hopper Run Checks.xlsx
+++ b/TELEMETRYadcCLOCK/project/Post Hopper Run Checks.xlsx
@@ -9,24 +9,23 @@
   <sheets>
     <sheet name="No Zero Net" sheetId="1" r:id="rId1"/>
     <sheet name="Validate no &quot;text&quot; in Datamaps" sheetId="2" r:id="rId2"/>
-    <sheet name="Missing Bio Symbol Files" sheetId="3" r:id="rId3"/>
-    <sheet name="Missing Nets" sheetId="4" r:id="rId4"/>
-    <sheet name="Shorted Inputs" sheetId="5" r:id="rId5"/>
-    <sheet name="Shorted Outputs" sheetId="6" r:id="rId6"/>
-    <sheet name="Floating Inputs" sheetId="7" r:id="rId7"/>
-    <sheet name="Floating Outputs" sheetId="8" r:id="rId8"/>
-    <sheet name="No Connects - Outputs" sheetId="9" r:id="rId9"/>
-    <sheet name="No Connects - Inputs" sheetId="10" r:id="rId10"/>
-    <sheet name="Mixed Mode Conflicts" sheetId="11" r:id="rId11"/>
-    <sheet name="Ring Core IO check report" sheetId="12" r:id="rId12"/>
-    <sheet name="D to A Tree" sheetId="13" r:id="rId13"/>
+    <sheet name="Missing Nets" sheetId="3" r:id="rId3"/>
+    <sheet name="Shorted Inputs" sheetId="4" r:id="rId4"/>
+    <sheet name="Shorted Outputs" sheetId="5" r:id="rId5"/>
+    <sheet name="Floating Inputs" sheetId="6" r:id="rId6"/>
+    <sheet name="Floating Outputs" sheetId="7" r:id="rId7"/>
+    <sheet name="No Connects - Outputs" sheetId="8" r:id="rId8"/>
+    <sheet name="No Connects - Inputs" sheetId="9" r:id="rId9"/>
+    <sheet name="Mixed Mode Conflicts" sheetId="10" r:id="rId10"/>
+    <sheet name="Ring Core IO check report" sheetId="11" r:id="rId11"/>
+    <sheet name="D to A Tree" sheetId="12" r:id="rId12"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="26">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -55,16 +54,13 @@
     <t>Xdatamap1 (datamap.function) missing expected field datamap_function_2</t>
   </si>
   <si>
-    <t>Missing Bio Symbol Files</t>
-  </si>
-  <si>
-    <t>No missing bio or symbol files...</t>
-  </si>
-  <si>
     <t>Missing Nets</t>
   </si>
   <si>
-    <t>All symbols have nets.</t>
+    <t>(!!! MUST FIX !!! - makes Corrupted Verilogs)</t>
+  </si>
+  <si>
+    <t>Xoscillator1,CELREF</t>
   </si>
   <si>
     <t>Shorted Inputs</t>
@@ -82,13 +78,7 @@
     <t>Floating Inputs</t>
   </si>
   <si>
-    <t>(!!! MUST FIX !!! - not allowed)</t>
-  </si>
-  <si>
-    <t>XCLOCK</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.CELREF84329(CELREF84329)</t>
+    <t>No Floating Input Nets found.</t>
   </si>
   <si>
     <t>Floating Outputs</t>
@@ -101,9 +91,6 @@
   </si>
   <si>
     <t>No Connects - Inputs</t>
-  </si>
-  <si>
-    <t>CELREF84329 - {"path": "XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "CELREF84329", "io": "input", "bus": "", "type": "child"}</t>
   </si>
   <si>
     <t>Mixed Mode Conflicts</t>
@@ -481,87 +468,62 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>25</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1">
-      <c r="A4" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -611,7 +573,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -629,6 +591,16 @@
         <v>10</v>
       </c>
     </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -641,7 +613,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -651,7 +623,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -666,7 +638,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -676,7 +648,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -691,7 +663,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -701,7 +673,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -711,12 +683,12 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>17</v>
+  <dimension ref="A1:A5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -726,27 +698,37 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -759,31 +741,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/TELEMETRYadcCLOCK/project/Post Hopper Run Checks.xlsx
+++ b/TELEMETRYadcCLOCK/project/Post Hopper Run Checks.xlsx
@@ -10,22 +10,21 @@
     <sheet name="No Zero Net" sheetId="1" r:id="rId1"/>
     <sheet name="Validate no &quot;text&quot; in Datamaps" sheetId="2" r:id="rId2"/>
     <sheet name="Missing Nets" sheetId="3" r:id="rId3"/>
-    <sheet name="Shorted Inputs" sheetId="4" r:id="rId4"/>
-    <sheet name="Shorted Outputs" sheetId="5" r:id="rId5"/>
-    <sheet name="Floating Inputs" sheetId="6" r:id="rId6"/>
-    <sheet name="Floating Outputs" sheetId="7" r:id="rId7"/>
-    <sheet name="No Connects - Outputs" sheetId="8" r:id="rId8"/>
-    <sheet name="No Connects - Inputs" sheetId="9" r:id="rId9"/>
-    <sheet name="Mixed Mode Conflicts" sheetId="10" r:id="rId10"/>
-    <sheet name="Ring Core IO check report" sheetId="11" r:id="rId11"/>
-    <sheet name="D to A Tree" sheetId="12" r:id="rId12"/>
+    <sheet name="Shorted Nets" sheetId="4" r:id="rId4"/>
+    <sheet name="Floating Inputs" sheetId="5" r:id="rId5"/>
+    <sheet name="Floating Outputs" sheetId="6" r:id="rId6"/>
+    <sheet name="No Connects - Customer" sheetId="7" r:id="rId7"/>
+    <sheet name="No Connects - Celera" sheetId="8" r:id="rId8"/>
+    <sheet name="Mixed Mode Conflicts" sheetId="9" r:id="rId9"/>
+    <sheet name="Ring Core IO check report" sheetId="10" r:id="rId10"/>
+    <sheet name="D to A Tree" sheetId="11" r:id="rId11"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="28">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -63,34 +62,40 @@
     <t>Xoscillator1,CELREF</t>
   </si>
   <si>
-    <t>Shorted Inputs</t>
-  </si>
-  <si>
-    <t>No Shorted Input Nets found.</t>
-  </si>
-  <si>
-    <t>Shorted Outputs</t>
-  </si>
-  <si>
-    <t>No Shorted Output Nets found.</t>
+    <t>Shorted Nets</t>
+  </si>
+  <si>
+    <t>No Shorted Nets found.</t>
   </si>
   <si>
     <t>Floating Inputs</t>
   </si>
   <si>
-    <t>No Floating Input Nets found.</t>
+    <t>(!!! MUST FIX !!! - not allowed)</t>
+  </si>
+  <si>
+    <t>XCLOCK,XDEBUG</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.dft_clock(dft_clock)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.fault_adcclock(fault_adcclock)</t>
+  </si>
+  <si>
+    <t>Floating pin Xoscillator1.global_oscillatorring(tl0)</t>
   </si>
   <si>
     <t>Floating Outputs</t>
   </si>
   <si>
-    <t>No Floating Output Nets found.</t>
-  </si>
-  <si>
-    <t>No Connects - Outputs</t>
-  </si>
-  <si>
-    <t>No Connects - Inputs</t>
+    <t>No Connects - Customer</t>
+  </si>
+  <si>
+    <t>No Connects - Celera</t>
+  </si>
+  <si>
+    <t>XU1.pulse net: XUADCCLOCKstartup_no_dft_noconn_pulse io: output</t>
   </si>
   <si>
     <t>Mixed Mode Conflicts</t>
@@ -468,32 +473,12 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -508,22 +493,22 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>24</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+        <v>26</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -633,7 +618,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -651,6 +636,31 @@
         <v>15</v>
       </c>
     </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>19</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -658,17 +668,17 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
+  <dimension ref="A1:A9"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
         <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:1">
@@ -676,6 +686,21 @@
         <v>17</v>
       </c>
     </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>19</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -683,37 +708,57 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -724,24 +769,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>